--- a/siteid.xlsx
+++ b/siteid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PhD-UNR\Manuscripts\Katarena Matos\PhD Dissertation\Chapter 1\Submission to GRL\Public Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katar\Documents\PhD\Chapter 1\Response to Reviewers\Consolidating Final Versions\Public Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0CCCA9-8E4D-4287-A35B-31657BA4D344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A073B1-F55C-4834-9C7F-154F4D8FA437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5850" yWindow="525" windowWidth="22500" windowHeight="14760" xr2:uid="{57E9A73E-2626-41A6-ACAA-7810F079E365}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="21580" windowHeight="15200" xr2:uid="{57E9A73E-2626-41A6-ACAA-7810F079E365}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="95">
   <si>
     <t>CLBJ1</t>
   </si>
@@ -291,6 +291,36 @@
   </si>
   <si>
     <t>ONAQ10</t>
+  </si>
+  <si>
+    <t>ecosystem type</t>
+  </si>
+  <si>
+    <t>season</t>
+  </si>
+  <si>
+    <t>woodland</t>
+  </si>
+  <si>
+    <t>grassland</t>
+  </si>
+  <si>
+    <t>forest</t>
+  </si>
+  <si>
+    <t>alpine</t>
+  </si>
+  <si>
+    <t>shrub</t>
+  </si>
+  <si>
+    <t>Summer</t>
+  </si>
+  <si>
+    <t>Fall</t>
+  </si>
+  <si>
+    <t>Spring</t>
   </si>
 </sst>
 </file>
@@ -665,15 +695,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{433278B5-6EF2-4C2B-88AD-8A82A506A073}">
-  <dimension ref="A1:C57"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E57"/>
+  <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.69921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.0703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.35546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>46</v>
       </c>
@@ -683,8 +715,14 @@
       <c r="C1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -694,8 +732,14 @@
       <c r="C2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -705,8 +749,14 @@
       <c r="C3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -716,8 +766,14 @@
       <c r="C4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -727,8 +783,14 @@
       <c r="C5" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -738,8 +800,14 @@
       <c r="C6" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -749,8 +817,14 @@
       <c r="C7" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -760,8 +834,14 @@
       <c r="C8" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -771,8 +851,14 @@
       <c r="C9" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -782,8 +868,14 @@
       <c r="C10" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -793,8 +885,14 @@
       <c r="C11" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -804,8 +902,14 @@
       <c r="C12" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -815,8 +919,14 @@
       <c r="C13" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -826,8 +936,14 @@
       <c r="C14" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -837,8 +953,14 @@
       <c r="C15" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -848,8 +970,14 @@
       <c r="C16" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -859,8 +987,14 @@
       <c r="C17" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -870,8 +1004,14 @@
       <c r="C18" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -881,8 +1021,14 @@
       <c r="C19" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -892,8 +1038,14 @@
       <c r="C20" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -903,8 +1055,14 @@
       <c r="C21" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>20</v>
       </c>
@@ -914,8 +1072,14 @@
       <c r="C22" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -925,8 +1089,14 @@
       <c r="C23" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -936,8 +1106,14 @@
       <c r="C24" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -947,8 +1123,14 @@
       <c r="C25" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -958,8 +1140,14 @@
       <c r="C26" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -969,8 +1157,14 @@
       <c r="C27" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D27" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -980,8 +1174,14 @@
       <c r="C28" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D28" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -991,8 +1191,14 @@
       <c r="C29" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D29" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -1002,8 +1208,14 @@
       <c r="C30" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>29</v>
       </c>
@@ -1013,8 +1225,14 @@
       <c r="C31" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
+        <v>89</v>
+      </c>
+      <c r="E31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>30</v>
       </c>
@@ -1024,8 +1242,14 @@
       <c r="C32" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
+        <v>89</v>
+      </c>
+      <c r="E32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -1035,8 +1259,14 @@
       <c r="C33" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D33" t="s">
+        <v>89</v>
+      </c>
+      <c r="E33" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>32</v>
       </c>
@@ -1046,8 +1276,14 @@
       <c r="C34" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>33</v>
       </c>
@@ -1057,8 +1293,14 @@
       <c r="C35" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D35" t="s">
+        <v>89</v>
+      </c>
+      <c r="E35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -1068,8 +1310,14 @@
       <c r="C36" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -1079,8 +1327,14 @@
       <c r="C37" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E37" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>36</v>
       </c>
@@ -1090,8 +1344,14 @@
       <c r="C38" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D38" t="s">
+        <v>88</v>
+      </c>
+      <c r="E38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -1101,8 +1361,14 @@
       <c r="C39" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D39" t="s">
+        <v>88</v>
+      </c>
+      <c r="E39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>38</v>
       </c>
@@ -1112,8 +1378,14 @@
       <c r="C40" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D40" t="s">
+        <v>88</v>
+      </c>
+      <c r="E40" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -1123,8 +1395,14 @@
       <c r="C41" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41" t="s">
+        <v>88</v>
+      </c>
+      <c r="E41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -1134,8 +1412,14 @@
       <c r="C42" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D42" t="s">
+        <v>89</v>
+      </c>
+      <c r="E42" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -1145,8 +1429,14 @@
       <c r="C43" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D43" t="s">
+        <v>89</v>
+      </c>
+      <c r="E43" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>42</v>
       </c>
@@ -1156,8 +1446,14 @@
       <c r="C44" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D44" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -1167,8 +1463,14 @@
       <c r="C45" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D45" t="s">
+        <v>87</v>
+      </c>
+      <c r="E45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -1178,8 +1480,14 @@
       <c r="C46" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D46" t="s">
+        <v>87</v>
+      </c>
+      <c r="E46" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -1189,8 +1497,14 @@
       <c r="C47" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D47" t="s">
+        <v>87</v>
+      </c>
+      <c r="E47" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>75</v>
       </c>
@@ -1200,8 +1514,14 @@
       <c r="C48" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D48" t="s">
+        <v>91</v>
+      </c>
+      <c r="E48" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>76</v>
       </c>
@@ -1211,8 +1531,14 @@
       <c r="C49" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49" t="s">
+        <v>91</v>
+      </c>
+      <c r="E49" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -1222,8 +1548,14 @@
       <c r="C50" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D50" t="s">
+        <v>91</v>
+      </c>
+      <c r="E50" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>78</v>
       </c>
@@ -1233,8 +1565,14 @@
       <c r="C51" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D51" t="s">
+        <v>91</v>
+      </c>
+      <c r="E51" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>79</v>
       </c>
@@ -1244,8 +1582,14 @@
       <c r="C52" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52" t="s">
+        <v>91</v>
+      </c>
+      <c r="E52" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -1255,8 +1599,14 @@
       <c r="C53" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53" t="s">
+        <v>91</v>
+      </c>
+      <c r="E53" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>81</v>
       </c>
@@ -1266,8 +1616,14 @@
       <c r="C54" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54" t="s">
+        <v>91</v>
+      </c>
+      <c r="E54" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>82</v>
       </c>
@@ -1277,8 +1633,14 @@
       <c r="C55" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55" t="s">
+        <v>91</v>
+      </c>
+      <c r="E55" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>83</v>
       </c>
@@ -1288,8 +1650,14 @@
       <c r="C56" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D56" t="s">
+        <v>91</v>
+      </c>
+      <c r="E56" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>84</v>
       </c>
@@ -1298,6 +1666,12 @@
       </c>
       <c r="C57" t="s">
         <v>74</v>
+      </c>
+      <c r="D57" t="s">
+        <v>91</v>
+      </c>
+      <c r="E57" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
